--- a/outputs/kobra_analitica_gestion.xlsx
+++ b/outputs/kobra_analitica_gestion.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>gestor_id</t>
   </si>
@@ -53,84 +53,84 @@
     <t>IA01</t>
   </si>
   <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
     <t>G04</t>
   </si>
   <si>
+    <t>G09</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
     <t>G03</t>
   </si>
   <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>G09</t>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>G06</t>
   </si>
   <si>
     <t>G08</t>
   </si>
   <si>
-    <t>G07</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>G01</t>
-  </si>
-  <si>
-    <t>G10</t>
+    <t>G02</t>
   </si>
   <si>
     <t>G05</t>
   </si>
   <si>
-    <t>G06</t>
-  </si>
-  <si>
-    <t>G02</t>
-  </si>
-  <si>
     <t>Gestor IA02</t>
   </si>
   <si>
     <t>Gestor IA01</t>
   </si>
   <si>
+    <t>Gestor 11</t>
+  </si>
+  <si>
+    <t>Gestor 01</t>
+  </si>
+  <si>
     <t>Gestor 04</t>
   </si>
   <si>
+    <t>Gestor 09</t>
+  </si>
+  <si>
+    <t>Gestor 07</t>
+  </si>
+  <si>
+    <t>Gestor 12</t>
+  </si>
+  <si>
     <t>Gestor 03</t>
   </si>
   <si>
-    <t>Gestor 12</t>
-  </si>
-  <si>
-    <t>Gestor 09</t>
+    <t>Gestor 10</t>
+  </si>
+  <si>
+    <t>Gestor 06</t>
   </si>
   <si>
     <t>Gestor 08</t>
   </si>
   <si>
-    <t>Gestor 07</t>
-  </si>
-  <si>
-    <t>Gestor 11</t>
-  </si>
-  <si>
-    <t>Gestor 01</t>
-  </si>
-  <si>
-    <t>Gestor 10</t>
+    <t>Gestor 02</t>
   </si>
   <si>
     <t>Gestor 05</t>
   </si>
   <si>
-    <t>Gestor 06</t>
-  </si>
-  <si>
-    <t>Gestor 02</t>
-  </si>
-  <si>
     <t>calidad_inicial</t>
   </si>
   <si>
@@ -188,12 +188,6 @@
     <t>2026-06</t>
   </si>
   <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>inf</t>
-  </si>
-  <si>
     <t>tramo_mora</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
   </si>
   <si>
     <t>Corporativo</t>
-  </si>
-  <si>
-    <t>Desconocido</t>
   </si>
   <si>
     <t>Pyme</t>
@@ -620,22 +611,22 @@
         <v>840</v>
       </c>
       <c r="D2">
-        <v>83.973</v>
+        <v>84.001</v>
       </c>
       <c r="E2">
-        <v>69248494</v>
+        <v>61752431</v>
       </c>
       <c r="F2">
-        <v>129478740</v>
+        <v>130719970</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0.774</v>
+        <v>0.788</v>
       </c>
       <c r="I2">
-        <v>0.535</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -646,25 +637,25 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D3">
-        <v>83.777</v>
+        <v>83.798</v>
       </c>
       <c r="E3">
-        <v>55580935</v>
+        <v>59232845</v>
       </c>
       <c r="F3">
-        <v>119757140</v>
+        <v>135224810</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0.759</v>
+        <v>0.779</v>
       </c>
       <c r="I3">
-        <v>0.464</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -675,25 +666,25 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="D4">
-        <v>75.39400000000001</v>
+        <v>78.877</v>
       </c>
       <c r="E4">
-        <v>37666889</v>
+        <v>35302698</v>
       </c>
       <c r="F4">
-        <v>76705570</v>
+        <v>72552200</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0.755</v>
+        <v>0.74</v>
       </c>
       <c r="I4">
-        <v>0.491</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -704,25 +695,25 @@
         <v>26</v>
       </c>
       <c r="C5">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D5">
-        <v>73.22</v>
+        <v>64.76900000000001</v>
       </c>
       <c r="E5">
-        <v>35475125</v>
+        <v>33729750</v>
       </c>
       <c r="F5">
-        <v>75917050</v>
+        <v>76550600</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.733</v>
+        <v>0.646</v>
       </c>
       <c r="I5">
-        <v>0.467</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -733,25 +724,25 @@
         <v>27</v>
       </c>
       <c r="C6">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="D6">
-        <v>75.14</v>
+        <v>75.679</v>
       </c>
       <c r="E6">
-        <v>34093167</v>
+        <v>31715976</v>
       </c>
       <c r="F6">
-        <v>68232610</v>
+        <v>68189120</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0.754</v>
+        <v>0.713</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -765,22 +756,22 @@
         <v>471</v>
       </c>
       <c r="D7">
-        <v>67.13800000000001</v>
+        <v>67.562</v>
       </c>
       <c r="E7">
-        <v>31633466</v>
+        <v>31119095</v>
       </c>
       <c r="F7">
-        <v>68861150</v>
+        <v>70261110</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0.605</v>
+        <v>0.658</v>
       </c>
       <c r="I7">
-        <v>0.459</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -791,25 +782,25 @@
         <v>29</v>
       </c>
       <c r="C8">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="D8">
-        <v>64.45699999999999</v>
+        <v>69.072</v>
       </c>
       <c r="E8">
-        <v>31580546</v>
+        <v>30344073</v>
       </c>
       <c r="F8">
-        <v>87475510</v>
+        <v>69127790</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>0.619</v>
+        <v>0.671</v>
       </c>
       <c r="I8">
-        <v>0.361</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -820,25 +811,25 @@
         <v>30</v>
       </c>
       <c r="C9">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D9">
-        <v>69.559</v>
+        <v>74.73</v>
       </c>
       <c r="E9">
-        <v>30896368</v>
+        <v>28058488</v>
       </c>
       <c r="F9">
-        <v>63145260</v>
+        <v>67617180</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>0.675</v>
+        <v>0.674</v>
       </c>
       <c r="I9">
-        <v>0.489</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -849,25 +840,25 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D10">
-        <v>79.167</v>
+        <v>73.621</v>
       </c>
       <c r="E10">
-        <v>30775207</v>
+        <v>27407038</v>
       </c>
       <c r="F10">
-        <v>68493150</v>
+        <v>58670550</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="I10">
-        <v>0.449</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -878,25 +869,25 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="D11">
-        <v>63.824</v>
+        <v>61.92</v>
       </c>
       <c r="E11">
-        <v>28015532</v>
+        <v>27024036</v>
       </c>
       <c r="F11">
-        <v>74979340</v>
+        <v>62922910</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0.657</v>
+        <v>0.63</v>
       </c>
       <c r="I11">
-        <v>0.374</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -907,25 +898,25 @@
         <v>33</v>
       </c>
       <c r="C12">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D12">
-        <v>61.555</v>
+        <v>53.946</v>
       </c>
       <c r="E12">
-        <v>25146877</v>
+        <v>26285852</v>
       </c>
       <c r="F12">
-        <v>66876290</v>
+        <v>66644040</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>0.601</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I12">
-        <v>0.376</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -936,25 +927,25 @@
         <v>34</v>
       </c>
       <c r="C13">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D13">
-        <v>50.071</v>
+        <v>64.962</v>
       </c>
       <c r="E13">
-        <v>22196467</v>
+        <v>24947906</v>
       </c>
       <c r="F13">
-        <v>69382250</v>
+        <v>65419730</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0.531</v>
+        <v>0.644</v>
       </c>
       <c r="I13">
-        <v>0.32</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -965,25 +956,25 @@
         <v>35</v>
       </c>
       <c r="C14">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D14">
-        <v>53.653</v>
+        <v>52.288</v>
       </c>
       <c r="E14">
-        <v>21451311</v>
+        <v>21532128</v>
       </c>
       <c r="F14">
-        <v>59492300</v>
+        <v>70284980</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.584</v>
+        <v>0.547</v>
       </c>
       <c r="I14">
-        <v>0.361</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -994,25 +985,25 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D15">
-        <v>52.775</v>
+        <v>50.434</v>
       </c>
       <c r="E15">
-        <v>19181382</v>
+        <v>21442959</v>
       </c>
       <c r="F15">
-        <v>51606410</v>
+        <v>58034580</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="I15">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
     </row>
   </sheetData>
@@ -1056,350 +1047,350 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>43.1</v>
+        <v>54.4</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F2">
-        <v>14.9</v>
+        <v>12.7</v>
       </c>
       <c r="G2">
-        <v>0.452</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H2">
-        <v>0.654</v>
+        <v>0.678</v>
       </c>
       <c r="I2">
-        <v>0.202</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="E3">
-        <v>83.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F3">
-        <v>14.7</v>
+        <v>12.6</v>
       </c>
       <c r="G3">
-        <v>0.742</v>
+        <v>0.586</v>
       </c>
       <c r="H3">
-        <v>0.8120000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="I3">
-        <v>0.07000000000000001</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>54.2</v>
+        <v>71.3</v>
       </c>
       <c r="E4">
-        <v>68.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F4">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="G4">
-        <v>0.552</v>
+        <v>0.713</v>
       </c>
       <c r="H4">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="I4">
-        <v>0.098</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>60.8</v>
+        <v>44.4</v>
       </c>
       <c r="E5">
-        <v>74.2</v>
+        <v>56.2</v>
       </c>
       <c r="F5">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="G5">
-        <v>0.582</v>
+        <v>0.516</v>
       </c>
       <c r="H5">
-        <v>0.727</v>
+        <v>0.629</v>
       </c>
       <c r="I5">
-        <v>0.145</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="E6">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="F6">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G6">
-        <v>0.647</v>
+        <v>0.63</v>
       </c>
       <c r="H6">
-        <v>0.713</v>
+        <v>0.708</v>
       </c>
       <c r="I6">
-        <v>0.066</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>70.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E7">
-        <v>82.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F7">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="G7">
-        <v>0.752</v>
+        <v>0.725</v>
       </c>
       <c r="H7">
-        <v>0.789</v>
+        <v>0.828</v>
       </c>
       <c r="I7">
-        <v>0.037</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="E8">
-        <v>60.6</v>
+        <v>73</v>
       </c>
       <c r="F8">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="G8">
-        <v>0.492</v>
+        <v>0.582</v>
       </c>
       <c r="H8">
-        <v>0.6820000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="I8">
-        <v>0.19</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>68.40000000000001</v>
+        <v>59.1</v>
       </c>
       <c r="E9">
-        <v>79.8</v>
+        <v>70.3</v>
       </c>
       <c r="F9">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="G9">
-        <v>0.732</v>
+        <v>0.622</v>
       </c>
       <c r="H9">
-        <v>0.847</v>
+        <v>0.664</v>
       </c>
       <c r="I9">
-        <v>0.115</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>59.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E10">
-        <v>70.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F10">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>0.646</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H10">
-        <v>0.638</v>
+        <v>0.737</v>
       </c>
       <c r="I10">
-        <v>-0.008</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>72.8</v>
+        <v>49.1</v>
       </c>
       <c r="E11">
-        <v>83.2</v>
+        <v>60.1</v>
       </c>
       <c r="F11">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>0.583</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H11">
-        <v>0.739</v>
+        <v>0.556</v>
       </c>
       <c r="I11">
-        <v>0.156</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E12">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="F12">
         <v>0.3</v>
       </c>
       <c r="G12">
-        <v>0.551</v>
+        <v>0.63</v>
       </c>
       <c r="H12">
-        <v>0.635</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I12">
-        <v>0.08400000000000001</v>
+        <v>-0.067</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>63.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E13">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="F13">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.6840000000000001</v>
+        <v>0.662</v>
       </c>
       <c r="H13">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I13">
-        <v>-0.034</v>
+        <v>-0.052</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1446,22 +1437,22 @@
         <v>511</v>
       </c>
       <c r="C2">
-        <v>60.633</v>
+        <v>61.232</v>
       </c>
       <c r="D2">
-        <v>-0.061</v>
+        <v>-0.098</v>
       </c>
       <c r="E2">
-        <v>27669758</v>
+        <v>28233339</v>
       </c>
       <c r="F2">
-        <v>70929990</v>
+        <v>76563670</v>
       </c>
       <c r="G2">
-        <v>0.626</v>
+        <v>0.618</v>
       </c>
       <c r="H2">
-        <v>0.39</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1472,22 +1463,22 @@
         <v>502</v>
       </c>
       <c r="C3">
-        <v>60.487</v>
+        <v>60.822</v>
       </c>
       <c r="D3">
-        <v>-0.075</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E3">
-        <v>29746874</v>
+        <v>32828490</v>
       </c>
       <c r="F3">
-        <v>77458350</v>
+        <v>80201570</v>
       </c>
       <c r="G3">
-        <v>0.629</v>
+        <v>0.637</v>
       </c>
       <c r="H3">
-        <v>0.384</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1498,22 +1489,22 @@
         <v>515</v>
       </c>
       <c r="C4">
-        <v>60.448</v>
+        <v>60.405</v>
       </c>
       <c r="D4">
-        <v>-0.073</v>
+        <v>-0.09</v>
       </c>
       <c r="E4">
-        <v>26768785</v>
+        <v>22981604</v>
       </c>
       <c r="F4">
-        <v>60371900</v>
+        <v>66329050</v>
       </c>
       <c r="G4">
-        <v>0.606</v>
+        <v>0.616</v>
       </c>
       <c r="H4">
-        <v>0.443</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1524,22 +1515,22 @@
         <v>503</v>
       </c>
       <c r="C5">
-        <v>61.847</v>
+        <v>61.897</v>
       </c>
       <c r="D5">
-        <v>-0.033</v>
+        <v>-0.055</v>
       </c>
       <c r="E5">
-        <v>34796900</v>
+        <v>32035858</v>
       </c>
       <c r="F5">
-        <v>80216640</v>
+        <v>75792340</v>
       </c>
       <c r="G5">
-        <v>0.646</v>
+        <v>0.632</v>
       </c>
       <c r="H5">
-        <v>0.434</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1550,22 +1541,22 @@
         <v>515</v>
       </c>
       <c r="C6">
-        <v>63.454</v>
+        <v>64.505</v>
       </c>
       <c r="D6">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="E6">
-        <v>30139458</v>
+        <v>29181489</v>
       </c>
       <c r="F6">
-        <v>79615060</v>
+        <v>70353710</v>
       </c>
       <c r="G6">
-        <v>0.633</v>
+        <v>0.625</v>
       </c>
       <c r="H6">
-        <v>0.379</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1576,22 +1567,22 @@
         <v>508</v>
       </c>
       <c r="C7">
-        <v>66.38500000000001</v>
+        <v>66.42100000000001</v>
       </c>
       <c r="D7">
-        <v>-0.045</v>
+        <v>-0.065</v>
       </c>
       <c r="E7">
-        <v>23433111</v>
+        <v>32223253</v>
       </c>
       <c r="F7">
-        <v>72856850</v>
+        <v>76386840</v>
       </c>
       <c r="G7">
-        <v>0.618</v>
+        <v>0.648</v>
       </c>
       <c r="H7">
-        <v>0.322</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1602,22 +1593,22 @@
         <v>840</v>
       </c>
       <c r="C8">
-        <v>74.503</v>
+        <v>74.256</v>
       </c>
       <c r="D8">
-        <v>0.001</v>
+        <v>-0.019</v>
       </c>
       <c r="E8">
-        <v>64433898</v>
+        <v>53459111</v>
       </c>
       <c r="F8">
-        <v>142265630</v>
+        <v>134894310</v>
       </c>
       <c r="G8">
-        <v>0.696</v>
+        <v>0.671</v>
       </c>
       <c r="H8">
-        <v>0.453</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1628,19 +1619,19 @@
         <v>842</v>
       </c>
       <c r="C9">
-        <v>74.812</v>
+        <v>74.92</v>
       </c>
       <c r="D9">
-        <v>0.011</v>
+        <v>-0.013</v>
       </c>
       <c r="E9">
-        <v>60455407</v>
+        <v>51791451</v>
       </c>
       <c r="F9">
-        <v>125160080</v>
+        <v>107188460</v>
       </c>
       <c r="G9">
-        <v>0.728</v>
+        <v>0.732</v>
       </c>
       <c r="H9">
         <v>0.483</v>
@@ -1654,22 +1645,22 @@
         <v>833</v>
       </c>
       <c r="C10">
-        <v>75.06100000000001</v>
+        <v>75.036</v>
       </c>
       <c r="D10">
-        <v>-0.021</v>
+        <v>0.002</v>
       </c>
       <c r="E10">
-        <v>56120573</v>
+        <v>55068083</v>
       </c>
       <c r="F10">
-        <v>123916800</v>
+        <v>132258140</v>
       </c>
       <c r="G10">
-        <v>0.699</v>
+        <v>0.702</v>
       </c>
       <c r="H10">
-        <v>0.453</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1680,22 +1671,22 @@
         <v>840</v>
       </c>
       <c r="C11">
-        <v>76.61499999999999</v>
+        <v>76.321</v>
       </c>
       <c r="D11">
-        <v>-0.011</v>
+        <v>0.007</v>
       </c>
       <c r="E11">
-        <v>66020284</v>
+        <v>59036190</v>
       </c>
       <c r="F11">
-        <v>128016570</v>
+        <v>118949680</v>
       </c>
       <c r="G11">
-        <v>0.744</v>
+        <v>0.736</v>
       </c>
       <c r="H11">
-        <v>0.516</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1706,48 +1697,22 @@
         <v>850</v>
       </c>
       <c r="C12">
-        <v>75.938</v>
+        <v>76.188</v>
       </c>
       <c r="D12">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="E12">
-        <v>53328218</v>
+        <v>63056407</v>
       </c>
       <c r="F12">
-        <v>119594900</v>
+        <v>133301800</v>
       </c>
       <c r="G12">
-        <v>0.725</v>
+        <v>0.751</v>
       </c>
       <c r="H12">
-        <v>0.446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>64.2</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>28500</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>57</v>
+        <v>0.473</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1727,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1774,7 +1739,7 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1789,167 +1754,167 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2">
-        <v>2103</v>
+        <v>2071</v>
       </c>
       <c r="C2">
-        <v>69.65900000000001</v>
+        <v>69.80800000000001</v>
       </c>
       <c r="D2">
-        <v>0.199</v>
+        <v>0.188</v>
       </c>
       <c r="E2">
-        <v>3.498</v>
+        <v>3.495</v>
       </c>
       <c r="F2">
-        <v>176108013</v>
+        <v>153120680</v>
       </c>
       <c r="G2">
-        <v>330563200</v>
+        <v>291899300</v>
       </c>
       <c r="H2">
-        <v>0.761</v>
+        <v>0.753</v>
       </c>
       <c r="I2">
-        <v>0.533</v>
+        <v>0.525</v>
       </c>
       <c r="J2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="C3">
-        <v>70.18600000000001</v>
+        <v>70.032</v>
       </c>
       <c r="D3">
-        <v>-0.317</v>
+        <v>-0.331</v>
       </c>
       <c r="E3">
-        <v>3.466</v>
+        <v>3.495</v>
       </c>
       <c r="F3">
-        <v>22121212</v>
+        <v>22478154</v>
       </c>
       <c r="G3">
-        <v>95315280</v>
+        <v>96743070</v>
       </c>
       <c r="H3">
-        <v>0.504</v>
+        <v>0.517</v>
       </c>
       <c r="I3">
         <v>0.232</v>
       </c>
       <c r="J3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B4">
-        <v>1771</v>
+        <v>1838</v>
       </c>
       <c r="C4">
-        <v>69.489</v>
+        <v>70.136</v>
       </c>
       <c r="D4">
-        <v>0.101</v>
+        <v>0.089</v>
       </c>
       <c r="E4">
-        <v>3.497</v>
+        <v>3.514</v>
       </c>
       <c r="F4">
-        <v>104473017</v>
+        <v>121814628</v>
       </c>
       <c r="G4">
-        <v>228459790</v>
+        <v>264746580</v>
       </c>
       <c r="H4">
-        <v>0.725</v>
+        <v>0.736</v>
       </c>
       <c r="I4">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="C5">
-        <v>70.19499999999999</v>
+        <v>69.973</v>
       </c>
       <c r="D5">
-        <v>-0.157</v>
+        <v>-0.154</v>
       </c>
       <c r="E5">
-        <v>3.506</v>
+        <v>3.489</v>
       </c>
       <c r="F5">
-        <v>74071299</v>
+        <v>79124690</v>
       </c>
       <c r="G5">
-        <v>162093480</v>
+        <v>186005360</v>
       </c>
       <c r="H5">
-        <v>0.6820000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="I5">
-        <v>0.457</v>
+        <v>0.425</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6">
-        <v>1556</v>
+        <v>1534</v>
       </c>
       <c r="C6">
-        <v>70.07599999999999</v>
+        <v>69.92700000000001</v>
       </c>
       <c r="D6">
-        <v>-0.25</v>
+        <v>-0.249</v>
       </c>
       <c r="E6">
-        <v>3.511</v>
+        <v>3.484</v>
       </c>
       <c r="F6">
-        <v>96168225</v>
+        <v>83357123</v>
       </c>
       <c r="G6">
-        <v>263971020</v>
+        <v>232825260</v>
       </c>
       <c r="H6">
-        <v>0.593</v>
+        <v>0.602</v>
       </c>
       <c r="I6">
-        <v>0.364</v>
+        <v>0.358</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1959,12 +1924,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1976,7 +1941,7 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1991,135 +1956,103 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C2">
-        <v>70.068</v>
+        <v>69.996</v>
       </c>
       <c r="D2">
-        <v>-0.044</v>
+        <v>-0.057</v>
       </c>
       <c r="E2">
-        <v>3.453</v>
+        <v>3.538</v>
       </c>
       <c r="F2">
-        <v>277602721</v>
+        <v>265748113</v>
       </c>
       <c r="G2">
-        <v>619859410</v>
+        <v>617558370</v>
       </c>
       <c r="H2">
-        <v>0.668</v>
+        <v>0.667</v>
       </c>
       <c r="I2">
-        <v>0.448</v>
+        <v>0.43</v>
       </c>
       <c r="J2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3">
+        <v>2064</v>
+      </c>
+      <c r="C3">
+        <v>69.691</v>
+      </c>
+      <c r="D3">
+        <v>-0.022</v>
+      </c>
+      <c r="E3">
+        <v>3.462</v>
+      </c>
+      <c r="F3">
+        <v>127358028</v>
+      </c>
+      <c r="G3">
+        <v>301350440</v>
+      </c>
+      <c r="H3">
+        <v>0.679</v>
+      </c>
+      <c r="I3">
+        <v>0.423</v>
+      </c>
+      <c r="J3" t="s">
         <v>72</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>64.2</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>28500</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4">
-        <v>2079</v>
+        <v>4451</v>
       </c>
       <c r="C4">
-        <v>69.26300000000001</v>
+        <v>70.083</v>
       </c>
       <c r="D4">
-        <v>-0.031</v>
+        <v>-0.03</v>
       </c>
       <c r="E4">
-        <v>3.473</v>
+        <v>3.506</v>
       </c>
       <c r="F4">
-        <v>129193592</v>
+        <v>66789134</v>
       </c>
       <c r="G4">
-        <v>307640510</v>
+        <v>153310760</v>
       </c>
       <c r="H4">
-        <v>0.68</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I4">
-        <v>0.42</v>
+        <v>0.436</v>
       </c>
       <c r="J4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5">
-        <v>4431</v>
-      </c>
-      <c r="C5">
-        <v>70.078</v>
-      </c>
-      <c r="D5">
-        <v>-0.019</v>
-      </c>
-      <c r="E5">
-        <v>3.521</v>
-      </c>
-      <c r="F5">
-        <v>66116953</v>
-      </c>
-      <c r="G5">
-        <v>152902850</v>
-      </c>
-      <c r="H5">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="I5">
-        <v>0.432</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
